--- a/data/trans_orig/IQ19B_M_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ19B_M_R-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,32</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14,87</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22,5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,54</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,94</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,23</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13,23</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6,46</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16,14</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15,38</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,57</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.318251997738464</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>14.87088576832357</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>13.87105220584478</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>22.49927502574307</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5.541961433315256</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>16.94099230340034</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>17.2338089732881</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>13.2349272417736</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>6.462670885022664</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>16.14492252553475</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>15.38181554924171</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>17.57446145978494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,11; 10,74</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12,3; 21,5</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11,4; 18,87</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13,4; 57,72</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,92; 7,65</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,49; 20,31</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,63; 23,71</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11,0; 15,51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5,02; 8,37</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14,18; 19,2</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13,1; 19,23</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,29; 35,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>5.108022998939806</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>12.30121661083382</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>11.39702870743452</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>13.3953597040441</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.917758063024141</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>14.49456893286335</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>13.63455960667692</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>11.00148527559271</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>5.018858108706031</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>14.18293040858074</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>13.1033602963958</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>13.29206099336647</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.74461032157214</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>21.50020832957077</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>18.86979040463552</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>57.71597970134932</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>7.648289714789888</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>20.31282756700679</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>23.7082786667486</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>15.51067204371385</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8.367413928930446</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>19.20485296747938</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>19.2348725636761</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>35.64987931882878</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17,43</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15,22</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,06</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,2</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,95</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16,54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18,21</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14,61</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>16,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,35; 6,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15,26; 20,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13,95; 17,18</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14,55; 18,66</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,36; 6,17</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,7; 23,41</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,07; 15,53</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14,6; 19,72</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4,48; 5,85</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>16,69; 20,7</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13,78; 15,82</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,05; 18,16</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>5.146679262809149</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>17.42661877911086</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>15.21631444562906</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>16.06489916617933</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>5.151079546664557</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>19.20454650544941</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>13.95118993115909</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>16.54234518020575</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.148679831522129</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>18.21218684797626</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>14.61283571383043</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>16.28018565738932</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14,44</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15,66</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,87</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,8</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,51</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11,77</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4,09</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13,71</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>15,58</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,38</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4.354182647851913</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>15.26000705806979</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>13.94740844843249</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>14.54825281472143</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>4.361423675222243</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>16.69671778696689</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>13.0670597047484</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>14.5999035540811</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>4.481136344996125</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>16.69263505383259</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>13.77571976226345</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>15.05067879533701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,25; 5,97</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12,17; 17,14</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13,54; 19,81</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>11,25; 15,05</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,81; 5,32</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>11,64; 15,12</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,17; 19,27</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10,54; 13,57</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3,34; 5,18</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>12,42; 15,55</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>13,99; 17,97</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>11,2; 13,7</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.245330182158368</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>20.4599146894077</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>17.18061593242393</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>18.66277010702805</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>6.173557049632595</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>23.41238374865917</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>15.53477335962429</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>19.71854538758376</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5.850907627811758</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>20.69586412681433</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>15.8163962921258</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>18.16431498317118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16,62</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,16</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,84</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,53</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,57</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15,16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>17,05</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14,87</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,51</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.393507837375889</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>14.43766952292821</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>15.66424483563957</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>12.87253377918792</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.804965411575596</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>13.00188113297341</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>15.50717829885538</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>11.77299995480865</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>4.088864237757385</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>13.71372562540541</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>15.58032742652469</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>12.38486995435218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4,54; 6,08</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15,14; 19,29</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14,16; 16,57</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14,5; 18,62</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4,19; 5,55</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,74; 20,22</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13,61; 15,99</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13,91; 17,37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4,52; 5,53</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15,72; 18,53</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14,14; 15,75</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 16,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3.252494899501661</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>12.17320990359568</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>13.53745109479708</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>11.24619476762338</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>2.809355541978336</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>11.64216798497557</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>13.16893374167388</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>10.53657527569682</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>3.335694140517324</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>12.41674573593228</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>13.99380121944021</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>11.19998237796486</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.971453453675894</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>17.14159448385152</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>19.81401559606403</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>15.0466891820562</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>5.324387780891288</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>15.12009762663102</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>19.26670372089024</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>13.56959989240134</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>5.178371202599559</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>15.54870824352166</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>17.97282944422349</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>13.69785721705091</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.257441805556421</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>16.62213626510309</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>15.16089878880592</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>15.79725990456561</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>4.840115162562335</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>17.52537706017931</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>14.56846267517851</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>15.16493001610354</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5.059732520369197</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>17.05268512691747</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>14.87322135569804</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>15.50885210886059</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>4.542864402316569</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>15.1437234049553</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>14.16443763935187</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>14.50345925567899</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>4.190196599461815</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>15.73778305865504</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>13.60681025171699</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>13.9102562724371</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>4.521675179164869</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>15.72072337637544</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>14.14032320797529</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>14.44710219567274</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.081765081690304</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>19.2930269677885</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>16.57261392492364</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>18.62238795250728</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>5.551690363258229</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>20.21717679961819</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>15.98785553990637</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>17.36835498816781</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5.529403183945768</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>18.52972242268625</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>15.74783918042266</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>16.88593347316362</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
